--- a/testcases/simbench/1-LV-rural1--1-no_sw.xlsx
+++ b/testcases/simbench/1-LV-rural1--1-no_sw.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="12"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="bus"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="130">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -423,7 +423,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +441,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -487,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -515,6 +521,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -3215,7 +3227,7 @@
       </c>
       <c r="I1" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -5175,7 +5187,7 @@
     <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="8" width="23.14785714285714" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -5207,7 +5219,7 @@
       <c r="C1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -5349,8 +5361,8 @@
       <c r="C3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>69</v>
+      <c r="D3" s="11">
+        <v>1</v>
       </c>
       <c r="E3" s="7">
         <v>10</v>
@@ -5420,8 +5432,8 @@
       <c r="C4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>69</v>
+      <c r="D4" s="11">
+        <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>19</v>
@@ -5491,8 +5503,8 @@
       <c r="C5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>69</v>
+      <c r="D5" s="11">
+        <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>23</v>
@@ -5562,8 +5574,8 @@
       <c r="C6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>69</v>
+      <c r="D6" s="11">
+        <v>1</v>
       </c>
       <c r="E6" s="7">
         <v>24</v>
@@ -5633,8 +5645,8 @@
       <c r="C7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>69</v>
+      <c r="D7" s="11">
+        <v>1</v>
       </c>
       <c r="E7" s="7">
         <v>0</v>
@@ -5704,8 +5716,8 @@
       <c r="C8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>69</v>
+      <c r="D8" s="11">
+        <v>1</v>
       </c>
       <c r="E8" s="7">
         <v>24.5</v>
@@ -5775,8 +5787,8 @@
       <c r="C9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>69</v>
+      <c r="D9" s="11">
+        <v>1</v>
       </c>
       <c r="E9" s="7">
         <v>0</v>
